--- a/data/microseasons.xlsx
+++ b/data/microseasons.xlsx
@@ -23298,29 +23298,25 @@
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>Great horned owl</t>
+          <t>Jack-o'-lantern mushroom (Omphalotus illudens)</t>
         </is>
       </c>
       <c r="F5" s="26" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Great_Horned_Owl.USFWS.jpg</t>
+          <t>https://commons.wikimedia.org/wiki/File:Omphalotus_illudens_78007.jpg</t>
         </is>
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Great_Horned_Owl.USFWS.jpg?width=1600</t>
-        </is>
-      </c>
-      <c r="H5" s="26" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Great_Horned_Owl_%2831450031736%29.jpg</t>
-        </is>
-      </c>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Omphalotus_illudens_78007.jpg?width=1600</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="n"/>
       <c r="I5" s="25" t="n"/>
       <c r="J5" s="25" t="n"/>
       <c r="K5" s="25" t="inlineStr">
         <is>
-          <t>USFWS image, likely public domain</t>
+          <t>Swapped 2026-10-07 to a scientific close-up, per Laurie</t>
         </is>
       </c>
     </row>
@@ -24217,29 +24213,25 @@
       </c>
       <c r="E26" s="25" t="inlineStr">
         <is>
-          <t>Full moon rising</t>
+          <t>Full moon (Hunter's Moon)</t>
         </is>
       </c>
       <c r="F26" s="26" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Full_Moon_Rising_over_Diamond_Head_%284677896954%29.jpg</t>
+          <t>https://commons.wikimedia.org/wiki/File:Full_Moon_Luc_Viatour.jpg</t>
         </is>
       </c>
       <c r="G26" s="26" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Full_Moon_Rising_over_Diamond_Head_%284677896954%29.jpg?width=1600</t>
-        </is>
-      </c>
-      <c r="H26" s="26" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Landscape_with_Wheat_Sheaves_and_Rising_Moon_%28F735%29.jpg</t>
-        </is>
-      </c>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Full_Moon_Luc_Viatour.jpg?width=1600</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="n"/>
       <c r="I26" s="25" t="n"/>
       <c r="J26" s="25" t="n"/>
       <c r="K26" s="25" t="inlineStr">
         <is>
-          <t>Alternate is Van Gogh's moonrise over wheat sheaves (public domain)</t>
+          <t>Swapped 2026-10-07 to a scientific close-up, per Laurie</t>
         </is>
       </c>
     </row>
@@ -24307,27 +24299,27 @@
       </c>
       <c r="E28" s="25" t="inlineStr">
         <is>
-          <t>Sugar maple in autumn colour</t>
+          <t>Witch hazel in flower (Hamamelis virginiana)</t>
         </is>
       </c>
       <c r="F28" s="26" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Acer_saccharum_Equinox_Mountain_Vermont.jpg</t>
+          <t>https://commons.wikimedia.org/wiki/File:Hamamelis_virginiana_01.JPG</t>
         </is>
       </c>
       <c r="G28" s="26" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Acer_saccharum_Equinox_Mountain_Vermont.jpg?width=1600</t>
-        </is>
-      </c>
-      <c r="H28" s="26" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Sugar_maple_leaves_in_fall_-_Flickr_-_Muffet.jpg</t>
-        </is>
-      </c>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Hamamelis_virginiana_01.JPG?width=1600</t>
+        </is>
+      </c>
+      <c r="H28" s="26" t="n"/>
       <c r="I28" s="25" t="n"/>
       <c r="J28" s="25" t="n"/>
-      <c r="K28" s="25" t="n"/>
+      <c r="K28" s="25" t="inlineStr">
+        <is>
+          <t>Swapped 2026-10-07 to a scientific close-up, per Laurie</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="n">
@@ -24350,27 +24342,27 @@
       </c>
       <c r="E29" s="25" t="inlineStr">
         <is>
-          <t>Blue jay</t>
+          <t>Northern saw-whet owl (Aegolius acadicus)</t>
         </is>
       </c>
       <c r="F29" s="26" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Blue_Jay_RWD.jpg</t>
+          <t>https://commons.wikimedia.org/wiki/File:Aegolius_acadicus_(northern_saw-whet_owl).jpg</t>
         </is>
       </c>
       <c r="G29" s="26" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Blue_Jay_RWD.jpg?width=1600</t>
-        </is>
-      </c>
-      <c r="H29" s="26" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Cyanocitta-cristata-004.jpg</t>
-        </is>
-      </c>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Aegolius_acadicus_%28northern_saw-whet_owl%29.jpg?width=1600</t>
+        </is>
+      </c>
+      <c r="H29" s="26" t="n"/>
       <c r="I29" s="25" t="n"/>
       <c r="J29" s="25" t="n"/>
-      <c r="K29" s="25" t="n"/>
+      <c r="K29" s="25" t="inlineStr">
+        <is>
+          <t>Swapped 2026-10-07 to a scientific close-up, per Laurie</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="n">
@@ -29811,1033 +29803,1033 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Sun Dogs Over the Hills</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>January 1–15</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A5,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A5,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A5,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="G5" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A5,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A5,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I5">
+      <c r="I5" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A5,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J5">
+      <c r="J5" s="0">
         <f>SUM(D5:I5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Coyotes Court in the Blue Snow</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>January 16–31</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A6,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A6,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A6,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="G6" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A6,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A6,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I6">
+      <c r="I6" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A6,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <f>SUM(D6:I6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Owl Eggs in the Bitter Bright</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>February 1–15</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D7" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A7,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E7">
+      <c r="E7" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A7,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A7,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G7">
+      <c r="G7" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A7,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A7,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I7">
+      <c r="I7" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A7,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <f>SUM(D7:I7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Sap Stirs Under Bark</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>February 16–28</t>
         </is>
       </c>
-      <c r="D8">
+      <c r="D8" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A8,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E8">
+      <c r="E8" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A8,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A8,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G8">
+      <c r="G8" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A8,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H8">
+      <c r="H8" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A8,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I8">
+      <c r="I8" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A8,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J8">
+      <c r="J8" s="0">
         <f>SUM(D8:I8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="24">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Hazel Catkins Loosen</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>March 1–15</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D9" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A9,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E9">
+      <c r="E9" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A9,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A9,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G9">
+      <c r="G9" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A9,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H9">
+      <c r="H9" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A9,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I9">
+      <c r="I9" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A9,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <f>SUM(D9:I9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="24">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Redwings Climb the Hill</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>March 16–31</t>
         </is>
       </c>
-      <c r="D10">
+      <c r="D10" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A10,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E10">
+      <c r="E10" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A10,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F10">
+      <c r="F10" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A10,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G10">
+      <c r="G10" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A10,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H10">
+      <c r="H10" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A10,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I10">
+      <c r="I10" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A10,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J10">
+      <c r="J10" s="0">
         <f>SUM(D10:I10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="24">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Woodcock Sky Dance</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>April 1–15</t>
         </is>
       </c>
-      <c r="D11">
+      <c r="D11" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A11,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E11">
+      <c r="E11" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A11,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F11">
+      <c r="F11" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A11,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G11">
+      <c r="G11" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A11,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H11">
+      <c r="H11" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A11,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I11">
+      <c r="I11" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A11,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J11">
+      <c r="J11" s="0">
         <f>SUM(D11:I11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="24">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Peepers in the Cold Hollows</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>April 16–30</t>
         </is>
       </c>
-      <c r="D12">
+      <c r="D12" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A12,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E12">
+      <c r="E12" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A12,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="F12" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A12,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G12">
+      <c r="G12" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A12,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H12">
+      <c r="H12" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A12,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I12">
+      <c r="I12" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A12,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J12">
+      <c r="J12" s="0">
         <f>SUM(D12:I12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="24">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Green Fire in the Honeysuckle</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>May 1–15</t>
         </is>
       </c>
-      <c r="D13">
+      <c r="D13" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A13,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E13">
+      <c r="E13" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A13,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F13">
+      <c r="F13" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A13,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G13">
+      <c r="G13" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A13,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H13">
+      <c r="H13" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A13,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I13">
+      <c r="I13" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A13,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J13">
+      <c r="J13" s="0">
         <f>SUM(D13:I13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="24">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Chokecherry Snow</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>May 16–31</t>
         </is>
       </c>
-      <c r="D14">
+      <c r="D14" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A14,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E14">
+      <c r="E14" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A14,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F14">
+      <c r="F14" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A14,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G14">
+      <c r="G14" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A14,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H14">
+      <c r="H14" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A14,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I14">
+      <c r="I14" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A14,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J14">
+      <c r="J14" s="0">
         <f>SUM(D14:I14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="24">
-      <c r="A15" t="n">
+      <c r="A15" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Locust Perfume</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>June 1–15</t>
         </is>
       </c>
-      <c r="D15">
+      <c r="D15" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A15,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E15">
+      <c r="E15" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A15,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F15">
+      <c r="F15" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A15,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G15">
+      <c r="G15" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A15,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H15">
+      <c r="H15" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A15,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I15">
+      <c r="I15" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A15,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J15">
+      <c r="J15" s="0">
         <f>SUM(D15:I15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="24">
-      <c r="A16" t="n">
+      <c r="A16" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Dogwood Lace &amp; Fireflies</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>June 16–30</t>
         </is>
       </c>
-      <c r="D16">
+      <c r="D16" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A16,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E16">
+      <c r="E16" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A16,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F16">
+      <c r="F16" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A16,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G16">
+      <c r="G16" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A16,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H16">
+      <c r="H16" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A16,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I16">
+      <c r="I16" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A16,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J16">
+      <c r="J16" s="0">
         <f>SUM(D16:I16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="24">
-      <c r="A17" t="n">
+      <c r="A17" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Lavender &amp; Clearwing</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>July 1–15</t>
         </is>
       </c>
-      <c r="D17">
+      <c r="D17" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A17,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E17">
+      <c r="E17" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A17,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F17">
+      <c r="F17" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A17,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G17">
+      <c r="G17" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A17,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H17">
+      <c r="H17" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A17,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I17">
+      <c r="I17" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A17,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J17">
+      <c r="J17" s="0">
         <f>SUM(D17:I17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="24">
-      <c r="A18" t="n">
+      <c r="A18" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>Cicada Noon</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>July 16–31</t>
         </is>
       </c>
-      <c r="D18">
+      <c r="D18" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A18,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E18">
+      <c r="E18" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A18,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F18">
+      <c r="F18" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A18,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G18">
+      <c r="G18" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A18,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H18">
+      <c r="H18" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A18,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I18">
+      <c r="I18" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A18,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J18">
+      <c r="J18" s="0">
         <f>SUM(D18:I18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="24">
-      <c r="A19" t="n">
+      <c r="A19" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>Chokecherries Darken</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>August 1–15</t>
         </is>
       </c>
-      <c r="D19">
+      <c r="D19" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A19,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E19">
+      <c r="E19" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A19,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F19">
+      <c r="F19" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A19,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G19">
+      <c r="G19" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A19,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H19">
+      <c r="H19" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A19,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I19">
+      <c r="I19" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A19,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J19">
+      <c r="J19" s="0">
         <f>SUM(D19:I19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="24">
-      <c r="A20" t="n">
+      <c r="A20" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>Goldenrod Tide</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>August 16–31</t>
         </is>
       </c>
-      <c r="D20">
+      <c r="D20" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A20,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E20">
+      <c r="E20" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A20,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F20">
+      <c r="F20" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A20,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G20">
+      <c r="G20" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A20,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H20">
+      <c r="H20" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A20,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I20">
+      <c r="I20" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A20,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J20">
+      <c r="J20" s="0">
         <f>SUM(D20:I20)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="24">
-      <c r="A21" t="n">
+      <c r="A21" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>Hazel Harvest Moonrise</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>September 1–15</t>
         </is>
       </c>
-      <c r="D21">
+      <c r="D21" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A21,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E21">
+      <c r="E21" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A21,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F21">
+      <c r="F21" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A21,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G21">
+      <c r="G21" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A21,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H21">
+      <c r="H21" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A21,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I21">
+      <c r="I21" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A21,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J21">
+      <c r="J21" s="0">
         <f>SUM(D21:I21)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="24">
-      <c r="A22" t="n">
+      <c r="A22" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>Amber and Violet Waves</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>September 16–30</t>
         </is>
       </c>
-      <c r="D22">
+      <c r="D22" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A22,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E22">
+      <c r="E22" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A22,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F22">
+      <c r="F22" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A22,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G22">
+      <c r="G22" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A22,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H22">
+      <c r="H22" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A22,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I22">
+      <c r="I22" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A22,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J22">
+      <c r="J22" s="0">
         <f>SUM(D22:I22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="24">
-      <c r="A23" t="n">
+      <c r="A23" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Maple Blaze on the East Slope</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>October 1–15</t>
         </is>
       </c>
-      <c r="D23">
+      <c r="D23" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A23,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E23">
+      <c r="E23" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A23,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F23">
+      <c r="F23" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A23,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G23">
+      <c r="G23" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A23,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H23">
+      <c r="H23" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A23,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I23">
+      <c r="I23" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A23,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J23">
+      <c r="J23" s="0">
         <f>SUM(D23:I23)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="24">
-      <c r="A24" t="n">
+      <c r="A24" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Frost Flowers at First Hard Freeze</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>October 16–31</t>
         </is>
       </c>
-      <c r="D24">
+      <c r="D24" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A24,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E24">
+      <c r="E24" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A24,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F24">
+      <c r="F24" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A24,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G24">
+      <c r="G24" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A24,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H24">
+      <c r="H24" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A24,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I24">
+      <c r="I24" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A24,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J24">
+      <c r="J24" s="0">
         <f>SUM(D24:I24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="24">
-      <c r="A25" t="n">
+      <c r="A25" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Hair Ice on the Fallen Locust</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>November 1–15</t>
         </is>
       </c>
-      <c r="D25">
+      <c r="D25" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A25,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E25">
+      <c r="E25" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A25,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F25">
+      <c r="F25" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A25,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G25">
+      <c r="G25" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A25,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H25">
+      <c r="H25" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A25,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I25">
+      <c r="I25" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A25,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J25">
+      <c r="J25" s="0">
         <f>SUM(D25:I25)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="24">
-      <c r="A26" t="n">
+      <c r="A26" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>The Gray Time</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>November 16–30</t>
         </is>
       </c>
-      <c r="D26">
+      <c r="D26" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A26,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E26">
+      <c r="E26" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A26,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F26">
+      <c r="F26" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A26,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G26">
+      <c r="G26" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A26,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H26">
+      <c r="H26" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A26,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I26">
+      <c r="I26" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A26,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J26">
+      <c r="J26" s="0">
         <f>SUM(D26:I26)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="24">
-      <c r="A27" t="n">
+      <c r="A27" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>Snow Rollers on the Open Field</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>December 1–15</t>
         </is>
       </c>
-      <c r="D27">
+      <c r="D27" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A27,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E27">
+      <c r="E27" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A27,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F27">
+      <c r="F27" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A27,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G27">
+      <c r="G27" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A27,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H27">
+      <c r="H27" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A27,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I27">
+      <c r="I27" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A27,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J27">
+      <c r="J27" s="0">
         <f>SUM(D27:I27)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="24">
-      <c r="A28" t="n">
+      <c r="A28" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>Long Night on the Hills</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>December 16–31</t>
         </is>
       </c>
-      <c r="D28">
+      <c r="D28" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A28,'Entries (Long Form)'!$E$2:$E$2000,D$4)</f>
         <v/>
       </c>
-      <c r="E28">
+      <c r="E28" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A28,'Entries (Long Form)'!$E$2:$E$2000,E$4)</f>
         <v/>
       </c>
-      <c r="F28">
+      <c r="F28" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A28,'Entries (Long Form)'!$E$2:$E$2000,F$4)</f>
         <v/>
       </c>
-      <c r="G28">
+      <c r="G28" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A28,'Entries (Long Form)'!$E$2:$E$2000,G$4)</f>
         <v/>
       </c>
-      <c r="H28">
+      <c r="H28" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A28,'Entries (Long Form)'!$E$2:$E$2000,H$4)</f>
         <v/>
       </c>
-      <c r="I28">
+      <c r="I28" s="0">
         <f>COUNTIFS('Entries (Long Form)'!$A$2:$A$2000,$A28,'Entries (Long Form)'!$E$2:$E$2000,I$4)</f>
         <v/>
       </c>
-      <c r="J28">
+      <c r="J28" s="0">
         <f>SUM(D28:I28)</f>
         <v/>
       </c>
